--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484332_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484332_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2561</v>
+        <v>6.2523</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1344</v>
+        <v>4.8311</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1216</v>
+        <v>1.4212</v>
       </c>
       <c r="G2" t="n">
         <v>3.9112</v>
@@ -610,13 +610,13 @@
         <v>2.7348</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3291</v>
+        <v>0.3254</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2863</v>
+        <v>-0.017</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0428</v>
+        <v>0.3424</v>
       </c>
       <c r="V2" t="n">
         <v>-0.719</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4604</v>
+        <v>2.6276</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7863</v>
+        <v>2.7051</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6742</v>
+        <v>-0.0775</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6821</v>
+        <v>-0.3726</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6945</v>
+        <v>-1.0473</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.0124</v>
+        <v>0.6747</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2839</v>
+        <v>1.545</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7557</v>
+        <v>0.33</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4718</v>
+        <v>1.215</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6018</v>
+        <v>-1.9176</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0611</v>
+        <v>-1.3773</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5407</v>
+        <v>-0.5403</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9301</v>
+        <v>3.1255</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.5193</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8252</v>
+        <v>-0.3004</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6231</v>
+        <v>0.8198</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9962</v>
+        <v>0.3321</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.719</v>
+        <v>2.4373</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2772</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2965</v>
+        <v>2.3346</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4829</v>
+        <v>1.0689</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1865</v>
+        <v>1.2656</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3726</v>
+        <v>1.6821</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0473</v>
+        <v>2.6945</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6747</v>
+        <v>-1.0124</v>
       </c>
       <c r="J4" t="n">
-        <v>1.545</v>
+        <v>4.2839</v>
       </c>
       <c r="K4" t="n">
-        <v>0.33</v>
+        <v>4.7557</v>
       </c>
       <c r="L4" t="n">
-        <v>1.215</v>
+        <v>-0.4718</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9176</v>
+        <v>-2.6018</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3773</v>
+        <v>-2.0611</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5403</v>
+        <v>-0.5407</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1255</v>
+        <v>2.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1882</v>
+        <v>0.672</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5226</v>
+        <v>-0.5425</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7108</v>
+        <v>1.2145</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3321</v>
+        <v>-0.9962</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4373</v>
+        <v>-0.719</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1052</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0677</v>
+        <v>2.1343</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5134</v>
+        <v>2.6345</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4457</v>
+        <v>-0.5002</v>
       </c>
       <c r="G5" t="n">
         <v>1.1174</v>
@@ -844,13 +844,13 @@
         <v>2.5395</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0518</v>
+        <v>0.1183</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.5226</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6954</v>
+        <v>0.6409</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6642</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0413</v>
+        <v>0.1148</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8146</v>
+        <v>-0.5332</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8559</v>
+        <v>0.648</v>
       </c>
       <c r="G6" t="n">
-        <v>0.498</v>
+        <v>-0.997</v>
       </c>
       <c r="H6" t="n">
-        <v>0.768</v>
+        <v>0.8102</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.27</v>
+        <v>-1.8071</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9824000000000001</v>
+        <v>-0.1723</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9824000000000001</v>
+        <v>1.2292</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.4015</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4844</v>
+        <v>-0.8247</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2144</v>
+        <v>-0.419</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.27</v>
+        <v>-0.4056</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.5395</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5393</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1678</v>
+        <v>-0.3609</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3715</v>
+        <v>0.4291</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2163</v>
+        <v>-0.0413</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7554</v>
+        <v>0.8146</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5391</v>
+        <v>-0.8559</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.997</v>
+        <v>0.498</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8102</v>
+        <v>0.768</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8071</v>
+        <v>-0.27</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1723</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2292</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4015</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8247</v>
+        <v>-0.4844</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.419</v>
+        <v>-0.2144</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4056</v>
+        <v>-0.27</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.263</v>
+        <v>-0.5393</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5831</v>
+        <v>-0.1678</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3201</v>
+        <v>-0.3715</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4869</v>
+        <v>-0.3441</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7442</v>
+        <v>-0.7648</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2573</v>
+        <v>0.4207</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1764</v>
@@ -1078,13 +1078,13 @@
         <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1035</v>
+        <v>0.2463</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1294</v>
+        <v>0.1087</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0259</v>
+        <v>0.1375</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6093</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8576</v>
+        <v>-0.7426</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6194</v>
+        <v>-0.5589</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2382</v>
+        <v>-0.1837</v>
       </c>
       <c r="G9" t="n">
         <v>-0.638</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2196</v>
+        <v>-0.1046</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0138</v>
+        <v>0.0743</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2333</v>
+        <v>-0.1789</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0214</v>
+        <v>-0.9397</v>
       </c>
       <c r="E10" t="n">
         <v>-0.3222</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6992</v>
+        <v>-0.6175</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7732</v>
@@ -1234,13 +1234,13 @@
         <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4435</v>
+        <v>-0.3618</v>
       </c>
       <c r="T10" t="n">
         <v>-0.3631</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0803</v>
+        <v>0.0014</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5965</v>
+        <v>-1.0692</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6212</v>
+        <v>-2.2573</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0247</v>
+        <v>1.1881</v>
       </c>
       <c r="G11" t="n">
         <v>1.0432</v>
@@ -1312,13 +1312,13 @@
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6862</v>
+        <v>-0.1589</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4099</v>
+        <v>-0.046</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2763</v>
+        <v>-0.1129</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.518</v>
+        <v>-3.0761</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3033</v>
+        <v>-3.3439</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7852</v>
+        <v>0.2678</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1315</v>
@@ -1390,13 +1390,13 @@
         <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1213</v>
+        <v>0.5633</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1594</v>
+        <v>-0.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2808</v>
+        <v>0.7633</v>
       </c>
       <c r="V12" t="n">
         <v>0.0549</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.3427</v>
+        <v>7.250599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3659</v>
+        <v>4.273899999999998</v>
       </c>
       <c r="F13" t="n">
         <v>2.9766</v>
       </c>
       <c r="G13" t="n">
-        <v>3.163199999999999</v>
+        <v>3.163200000000001</v>
       </c>
       <c r="H13" t="n">
         <v>5.8634</v>
@@ -1468,13 +1468,13 @@
         <v>17.5809</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4401999999999999</v>
+        <v>1.3481</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.2452</v>
+        <v>-2.337299999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>3.6857</v>
+        <v>3.6856</v>
       </c>
       <c r="V13" t="n">
         <v>-4.0976</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2679</v>
+        <v>2.7784</v>
       </c>
       <c r="E14" t="n">
-        <v>2.201</v>
+        <v>3.4493</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0669</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6772</v>
+        <v>1.9558</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7043</v>
+        <v>-1.8347</v>
       </c>
       <c r="I14" t="n">
-        <v>0.027</v>
+        <v>3.7906</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0314</v>
+        <v>5.725</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0038</v>
+        <v>1.3942</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0276</v>
+        <v>4.3308</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7087</v>
+        <v>-3.7692</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7081</v>
+        <v>-3.229</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.5403</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9489</v>
+        <v>0.2366</v>
       </c>
       <c r="T14" t="n">
-        <v>2.537</v>
+        <v>-0.7716</v>
       </c>
       <c r="U14" t="n">
-        <v>0.412</v>
+        <v>1.0081</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9962</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6093</v>
+        <v>-0.3321</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3869</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9356</v>
+        <v>1.4271</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8426</v>
+        <v>0.2798</v>
       </c>
       <c r="F15" t="n">
-        <v>0.093</v>
+        <v>1.1473</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9558</v>
+        <v>-0.6772</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.8347</v>
+        <v>-0.7043</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7906</v>
+        <v>0.027</v>
       </c>
       <c r="J15" t="n">
-        <v>5.725</v>
+        <v>0.0314</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3942</v>
+        <v>0.0038</v>
       </c>
       <c r="L15" t="n">
-        <v>4.3308</v>
+        <v>0.0276</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.7692</v>
+        <v>-0.7087</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.229</v>
+        <v>-0.7081</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5403</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3938</v>
+        <v>1.1081</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3782</v>
+        <v>0.6158</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7721</v>
+        <v>0.4923</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.9962</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3321</v>
+        <v>0.6093</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3321</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.64</v>
+        <v>1.2822</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2447</v>
+        <v>1.9413</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6046</v>
+        <v>-0.6591</v>
       </c>
       <c r="G16" t="n">
         <v>0.0374</v>
@@ -1702,13 +1702,13 @@
         <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4892</v>
+        <v>0.1314</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2805</v>
+        <v>-0.5838</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>0.3321</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. TABERNER PERALTA</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6906</v>
+        <v>0.9825</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1817</v>
+        <v>-0.3043</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4911</v>
+        <v>1.2868</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5582</v>
+        <v>1.6148</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7355</v>
+        <v>1.075</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8227</v>
+        <v>0.5399</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3633</v>
+        <v>2.6628</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6754</v>
+        <v>2.6618</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6879</v>
+        <v>0.001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1949</v>
+        <v>-1.048</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0601</v>
+        <v>-1.5868</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1348</v>
+        <v>0.5389</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>0.351</v>
+        <v>0.2662</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1816</v>
+        <v>-0.1189</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5326</v>
+        <v>0.385</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>P. TABERNER PERALTA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3652</v>
+        <v>0.7839</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4054</v>
+        <v>1.3839</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7707000000000001</v>
+        <v>-0.6</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6148</v>
+        <v>1.5582</v>
       </c>
       <c r="H18" t="n">
-        <v>1.075</v>
+        <v>0.7355</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5399</v>
+        <v>0.8227</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6628</v>
+        <v>1.3633</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6618</v>
+        <v>0.6754</v>
       </c>
       <c r="L18" t="n">
-        <v>0.001</v>
+        <v>0.6879</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.048</v>
+        <v>0.1949</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5868</v>
+        <v>0.0601</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5389</v>
+        <v>0.1348</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.351</v>
+        <v>0.4443</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.22</v>
+        <v>0.0207</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1311</v>
+        <v>0.4237</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6642</v>
+        <v>-1.2186</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3869</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1597</v>
+        <v>0.3217</v>
       </c>
       <c r="E19" t="n">
         <v>-0.7747000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9343</v>
+        <v>1.0964</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2492</v>
@@ -1936,13 +1936,13 @@
         <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1772</v>
+        <v>-0.0151</v>
       </c>
       <c r="T19" t="n">
         <v>-0.121</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0561</v>
+        <v>0.1059</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.083</v>
+        <v>0.2929</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0629</v>
+        <v>1.4673</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1458</v>
+        <v>-1.1744</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2024</v>
@@ -2014,13 +2014,13 @@
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2713</v>
+        <v>0.1046</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6657</v>
+        <v>-0.2613</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3944</v>
+        <v>0.3658</v>
       </c>
       <c r="V20" t="n">
         <v>0.6093</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7478</v>
+        <v>-0.5041</v>
       </c>
       <c r="E21" t="n">
         <v>-0.397</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3509</v>
+        <v>-0.1071</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3087</v>
@@ -2092,13 +2092,13 @@
         <v>0.1953</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4391</v>
+        <v>-0.1953</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2421</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.197</v>
+        <v>0.0467</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7054</v>
+        <v>-2.7667</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3023</v>
+        <v>-2.7968</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.403</v>
+        <v>0.03</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0795</v>
@@ -2170,13 +2170,13 @@
         <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8678</v>
+        <v>0.0709</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6657</v>
+        <v>-0.1602</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.202</v>
+        <v>0.231</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3543</v>
+        <v>-3.9083</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9708</v>
+        <v>-2.7686</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3835</v>
+        <v>-1.1397</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2032</v>
@@ -2248,13 +2248,13 @@
         <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.248</v>
+        <v>-0.802</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0289</v>
+        <v>-0.8267</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2191</v>
+        <v>0.0246</v>
       </c>
       <c r="V23" t="n">
         <v>0.8317</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.5114</v>
+        <v>-5.6841</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6594</v>
+        <v>-4.4572</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.852</v>
+        <v>-1.2269</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6091</v>
@@ -2326,13 +2326,13 @@
         <v>1.5627</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2689</v>
+        <v>-0.4416</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.4388</v>
+        <v>-1.2365</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1699</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>1.8828</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.342899999999999</v>
+        <v>-4.9945</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.976700000000001</v>
+        <v>-2.977000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.366</v>
+        <v>-2.0176</v>
       </c>
       <c r="G25" t="n">
         <v>-3.1631</v>
@@ -2380,7 +2380,7 @@
         <v>12.3612</v>
       </c>
       <c r="K25" t="n">
-        <v>8.3078</v>
+        <v>8.307799999999999</v>
       </c>
       <c r="L25" t="n">
         <v>4.053399999999999</v>
@@ -2404,13 +2404,13 @@
         <v>10.7438</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4403999999999997</v>
+        <v>0.9080999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.6855</v>
+        <v>-3.6856</v>
       </c>
       <c r="U25" t="n">
-        <v>3.2454</v>
+        <v>4.5932</v>
       </c>
       <c r="V25" t="n">
         <v>4.0977</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484332_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484332_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,45 +714,50 @@
       </c>
       <c r="X3" t="n">
         <v>-2.1052</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3346</v>
+        <v>2.0276</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0689</v>
+        <v>0.762</v>
       </c>
       <c r="F4" t="n">
         <v>1.2656</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6821</v>
+        <v>1.3751</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6945</v>
+        <v>2.3875</v>
       </c>
       <c r="I4" t="n">
         <v>-1.0124</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2839</v>
+        <v>3.9769</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7557</v>
+        <v>4.4487</v>
       </c>
       <c r="L4" t="n">
         <v>-0.4718</v>
@@ -782,6 +797,11 @@
       </c>
       <c r="X4" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -792,203 +812,213 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1343</v>
+        <v>1.5279</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6345</v>
+        <v>1.5279</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5002</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1174</v>
+        <v>1.5279</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8376</v>
+        <v>0.921</v>
       </c>
       <c r="I5" t="n">
-        <v>1.955</v>
+        <v>0.607</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5793</v>
+        <v>1.5279</v>
       </c>
       <c r="K5" t="n">
-        <v>0.949</v>
+        <v>0.921</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6303</v>
+        <v>0.607</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4619</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7866</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6753</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1183</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5226</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6409</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1148</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5332</v>
+        <v>1.1065</v>
       </c>
       <c r="F6" t="n">
-        <v>0.648</v>
+        <v>-0.5002</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.997</v>
+        <v>-0.4106</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8102</v>
+        <v>-1.7586</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8071</v>
+        <v>1.348</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1723</v>
+        <v>2.0514</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2292</v>
+        <v>0.0281</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4015</v>
+        <v>2.0233</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8247</v>
+        <v>-2.4619</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.419</v>
+        <v>-1.7866</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4056</v>
+        <v>-0.6753</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5395</v>
+        <v>1.5627</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
         <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.1183</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3609</v>
+        <v>-0.5226</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4291</v>
+        <v>0.6409</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4959</v>
+        <v>-0.6642</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0413</v>
+        <v>0.307</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8146</v>
+        <v>0.307</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8559</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.498</v>
+        <v>0.307</v>
       </c>
       <c r="H7" t="n">
-        <v>0.768</v>
+        <v>0.307</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.307</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.307</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4844</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2144</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1000,13 +1030,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5393</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1678</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3715</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1016,135 +1046,145 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3441</v>
+        <v>0.1148</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7648</v>
+        <v>-0.5332</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4207</v>
+        <v>0.648</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1764</v>
+        <v>-0.997</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2167</v>
+        <v>0.8102</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0403</v>
+        <v>-1.8071</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1031</v>
+        <v>-0.1723</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06270000000000001</v>
+        <v>1.2292</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0405</v>
+        <v>-1.4015</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2795</v>
+        <v>-0.8247</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2793</v>
+        <v>-0.419</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0002</v>
+        <v>-0.4056</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>2.5395</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>2.5395</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2463</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1087</v>
+        <v>-0.3609</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1375</v>
+        <v>0.4291</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6093</v>
+        <v>-1.4959</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6093</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7426</v>
+        <v>-0.0413</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5589</v>
+        <v>0.8146</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1837</v>
+        <v>-0.8559</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.638</v>
+        <v>0.498</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.638</v>
+        <v>0.768</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.27</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6332</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6332</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0049</v>
+        <v>-0.4844</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0049</v>
+        <v>-0.2144</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.27</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1196,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1046</v>
+        <v>-0.5393</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0743</v>
+        <v>-0.1678</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1789</v>
+        <v>-0.3715</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1172,153 +1212,163 @@
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. LLUCIÀ MONSÓ</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9397</v>
+        <v>-0.3441</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3222</v>
+        <v>-0.7648</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6175</v>
+        <v>0.4207</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7732</v>
+        <v>-0.1764</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3684</v>
+        <v>-0.2167</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4049</v>
+        <v>0.0403</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0409</v>
+        <v>0.1031</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0409</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8142</v>
+        <v>-0.2795</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4093</v>
+        <v>-0.2793</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4049</v>
+        <v>-0.0002</v>
       </c>
       <c r="P10" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3618</v>
+        <v>0.2463</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3631</v>
+        <v>0.1087</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0014</v>
+        <v>0.1375</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0692</v>
+        <v>-0.7426</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2573</v>
+        <v>-0.5589</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1881</v>
+        <v>-0.1837</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0432</v>
+        <v>-0.638</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2571</v>
+        <v>-0.638</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7188</v>
+        <v>-0.6332</v>
       </c>
       <c r="K11" t="n">
-        <v>2.067</v>
+        <v>-0.6332</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3482</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3243</v>
+        <v>-0.0049</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1901</v>
+        <v>-0.0049</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1342</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1589</v>
+        <v>-0.1046</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.046</v>
+        <v>0.0743</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1129</v>
+        <v>-0.1789</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1328,324 +1378,345 @@
       </c>
       <c r="X11" t="n">
         <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>M. LLUCIA MONSO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0761</v>
+        <v>-0.9397</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3439</v>
+        <v>-0.3222</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2678</v>
+        <v>-0.6175</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1315</v>
+        <v>-0.7732</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6344</v>
+        <v>-0.3684</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.497</v>
+        <v>-0.4049</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2137</v>
+        <v>0.0409</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4733</v>
+        <v>0.0409</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6869</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9178</v>
+        <v>-0.8142</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1077</v>
+        <v>-0.4093</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8101</v>
+        <v>-0.4049</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5633</v>
+        <v>-0.3618</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2</v>
+        <v>-0.3631</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7633</v>
+        <v>0.0014</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0549</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.250599999999999</v>
+        <v>-1.0692</v>
       </c>
       <c r="E13" t="n">
-        <v>4.273899999999998</v>
+        <v>-2.2573</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9766</v>
+        <v>1.1881</v>
       </c>
       <c r="G13" t="n">
-        <v>3.163200000000001</v>
+        <v>1.0432</v>
       </c>
       <c r="H13" t="n">
-        <v>5.8634</v>
+        <v>2.2571</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.7002</v>
+        <v>-1.214</v>
       </c>
       <c r="J13" t="n">
-        <v>15.5241</v>
+        <v>0.7188</v>
       </c>
       <c r="K13" t="n">
-        <v>14.171</v>
+        <v>2.067</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3532</v>
+        <v>-1.3482</v>
       </c>
       <c r="M13" t="n">
-        <v>-12.3612</v>
+        <v>0.3243</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.307500000000001</v>
+        <v>0.1901</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.053599999999999</v>
+        <v>0.1342</v>
       </c>
       <c r="P13" t="n">
-        <v>6.837</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.7437</v>
+        <v>-2.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>17.5809</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3481</v>
+        <v>-0.1589</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.337299999999999</v>
+        <v>-0.046</v>
       </c>
       <c r="U13" t="n">
-        <v>3.6856</v>
+        <v>-0.1129</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.0976</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.831</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.9285</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7784</v>
+        <v>-3.0761</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4493</v>
+        <v>-3.3439</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6709000000000001</v>
+        <v>0.2678</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9558</v>
+        <v>-2.1315</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.8347</v>
+        <v>-0.6344</v>
       </c>
       <c r="I14" t="n">
-        <v>3.7906</v>
+        <v>-1.497</v>
       </c>
       <c r="J14" t="n">
-        <v>5.725</v>
+        <v>-0.2137</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3942</v>
+        <v>0.4733</v>
       </c>
       <c r="L14" t="n">
-        <v>4.3308</v>
+        <v>-0.6869</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.7692</v>
+        <v>-1.9178</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.229</v>
+        <v>-1.1077</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5403</v>
+        <v>-0.8101</v>
       </c>
       <c r="P14" t="n">
-        <v>0.586</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2366</v>
+        <v>0.5633</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7716</v>
+        <v>-0.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0081</v>
+        <v>0.7633</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.0549</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3321</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4271</v>
+        <v>7.2506</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2798</v>
+        <v>4.273900000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1473</v>
+        <v>2.9766</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6772</v>
+        <v>3.1631</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7043</v>
+        <v>5.8634</v>
       </c>
       <c r="I15" t="n">
-        <v>0.027</v>
+        <v>-2.7002</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0314</v>
+        <v>15.5241</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0038</v>
+        <v>14.1711</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0276</v>
+        <v>1.3532</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7087</v>
+        <v>-12.3612</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7081</v>
+        <v>-8.307500000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-4.0536</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>6.836999999999998</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-10.7437</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>17.5809</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1081</v>
+        <v>1.3481</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6158</v>
+        <v>-2.3373</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4923</v>
+        <v>3.6856</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9962</v>
+        <v>-4.0976</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6093</v>
+        <v>1.831</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3869</v>
-      </c>
+        <v>-5.928500000000001</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VALLES OLIVER</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2822</v>
+        <v>2.7784</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9413</v>
+        <v>3.4493</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6591</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0374</v>
+        <v>1.9558</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6572</v>
+        <v>-1.8347</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6198</v>
+        <v>3.7906</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4433</v>
+        <v>5.725</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9279</v>
+        <v>1.3942</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4846</v>
+        <v>4.3308</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4059</v>
+        <v>-3.7692</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2707</v>
+        <v>-3.229</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1352</v>
+        <v>-0.5403</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1314</v>
+        <v>0.2366</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5838</v>
+        <v>-0.7716</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7151999999999999</v>
+        <v>1.0081</v>
       </c>
       <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="X16" t="n">
         <v>0.3321</v>
       </c>
-      <c r="W16" t="n">
-        <v>0.2772</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.0549</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9825</v>
+        <v>1.4271</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3043</v>
+        <v>0.2798</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2868</v>
+        <v>1.1473</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6148</v>
+        <v>-0.6772</v>
       </c>
       <c r="H17" t="n">
-        <v>1.075</v>
+        <v>-0.7043</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5399</v>
+        <v>0.027</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6628</v>
+        <v>0.0314</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6618</v>
+        <v>0.0038</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001</v>
+        <v>0.0276</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.048</v>
+        <v>-0.7087</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5868</v>
+        <v>-0.7081</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5389</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2662</v>
+        <v>1.1081</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1189</v>
+        <v>0.6158</v>
       </c>
       <c r="U17" t="n">
-        <v>0.385</v>
+        <v>0.4923</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6642</v>
+        <v>0.9962</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X17" t="n">
         <v>0.3869</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. TABERNER PERALTA</t>
+          <t>J. VALLES OLIVER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7839</v>
+        <v>1.2822</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3839</v>
+        <v>1.9413</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6</v>
+        <v>-0.6591</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5582</v>
+        <v>0.0374</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7355</v>
+        <v>0.6572</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8227</v>
+        <v>-0.6198</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3633</v>
+        <v>2.4433</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6754</v>
+        <v>2.9279</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6879</v>
+        <v>-0.4846</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1949</v>
+        <v>-2.4059</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0601</v>
+        <v>-2.2707</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1348</v>
+        <v>-0.1352</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4443</v>
+        <v>0.1314</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0207</v>
+        <v>-0.5838</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4237</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2186</v>
+        <v>0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3217</v>
+        <v>0.9825</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-0.3043</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0964</v>
+        <v>1.2868</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2492</v>
+        <v>1.6148</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5188</v>
+        <v>1.075</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2696</v>
+        <v>0.5399</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6536</v>
+        <v>2.6628</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6536</v>
+        <v>2.6618</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4045</v>
+        <v>-1.048</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1348</v>
+        <v>-1.5868</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2696</v>
+        <v>0.5389</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0151</v>
+        <v>0.2662</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.121</v>
+        <v>-0.1189</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1059</v>
+        <v>0.385</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. PONS AVECILLAS</t>
+          <t>P. TABERNER PERALTA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2929</v>
+        <v>0.7839</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4673</v>
+        <v>1.3839</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1744</v>
+        <v>-0.6</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2024</v>
+        <v>1.5582</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1865</v>
+        <v>0.7355</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3889</v>
+        <v>0.8227</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1193</v>
+        <v>1.3633</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6987</v>
+        <v>0.6754</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5794</v>
+        <v>0.6879</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3217</v>
+        <v>0.1949</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5121</v>
+        <v>0.0601</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8095</v>
+        <v>0.1348</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1046</v>
+        <v>0.4443</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2613</v>
+        <v>0.0207</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3658</v>
+        <v>0.4237</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. VILLALON CAYETANO</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2143,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5041</v>
+        <v>0.3217</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.397</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1071</v>
+        <v>1.0964</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3087</v>
+        <v>-0.2492</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.484</v>
+        <v>-0.5188</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1753</v>
+        <v>0.2696</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0405</v>
+        <v>-0.6536</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-0.6536</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3492</v>
+        <v>0.4045</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.484</v>
+        <v>0.1348</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1348</v>
+        <v>0.2696</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1953</v>
+        <v>-0.0151</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2421</v>
+        <v>-0.121</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0467</v>
+        <v>0.1059</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2108,12 +2204,17 @@
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. REBOLLO BONET</t>
+          <t>S. PONS AVECILLAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7667</v>
+        <v>0.2929</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7968</v>
+        <v>1.4673</v>
       </c>
       <c r="F22" t="n">
-        <v>0.03</v>
+        <v>-1.1744</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0795</v>
+        <v>-1.2024</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4976</v>
+        <v>0.1865</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4181</v>
+        <v>-1.3889</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9251</v>
+        <v>1.1193</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9389</v>
+        <v>1.6987</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0138</v>
+        <v>-0.5794</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1544</v>
+        <v>-2.3217</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5587</v>
+        <v>-1.5121</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4043</v>
+        <v>-0.8095</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0709</v>
+        <v>0.1046</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1602</v>
+        <v>-0.2613</v>
       </c>
       <c r="U22" t="n">
-        <v>0.231</v>
+        <v>0.3658</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>C. VILLALON CAYETANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9083</v>
+        <v>-0.5041</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7686</v>
+        <v>-0.397</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1397</v>
+        <v>-0.1071</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2032</v>
+        <v>-0.3087</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1896</v>
+        <v>-0.484</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0136</v>
+        <v>0.1753</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1333</v>
+        <v>0.0405</v>
       </c>
       <c r="K23" t="n">
-        <v>0.472</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6613</v>
+        <v>0.0405</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3364</v>
+        <v>-0.3492</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6615</v>
+        <v>-0.484</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.1348</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.7348</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.9069</v>
+        <v>-0.1953</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.802</v>
+        <v>-0.1953</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8267</v>
+        <v>-0.2421</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0246</v>
+        <v>0.0467</v>
       </c>
       <c r="V23" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>A. REBOLLO BONET</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6841</v>
+        <v>-2.7667</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4572</v>
+        <v>-2.7968</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2269</v>
+        <v>0.03</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.6091</v>
+        <v>-1.0795</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.2886</v>
+        <v>-1.4976</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3206</v>
+        <v>0.4181</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.579</v>
+        <v>-0.9251</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0665</v>
+        <v>-0.9389</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6455</v>
+        <v>0.0138</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.0301</v>
+        <v>-0.1544</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.3551</v>
+        <v>-0.5587</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6751</v>
+        <v>0.4043</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.5162</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.0789</v>
+        <v>-2.9301</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4416</v>
+        <v>0.0709</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2365</v>
+        <v>-0.1602</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.231</v>
       </c>
       <c r="V24" t="n">
-        <v>1.8828</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.4373</v>
+        <v>1.2186</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,235 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-3.9083</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.7686</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.1397</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.2032</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.1896</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.0136</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.1333</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.3364</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.6615</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.6749000000000001</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-2.7348</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.802</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.8267</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.8317</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.8317</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>E. ZUSTOVICH</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-5.6841</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-4.4572</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.2269</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-3.6091</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-2.2886</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.3206</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.579</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0665</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.6455</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-3.0301</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-2.3551</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.6751</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-3.5162</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-5.0789</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.4416</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-1.2365</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.7949000000000001</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.8828</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.4373</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484332_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>-4.9945</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E27" t="n">
         <v>-2.977000000000001</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F27" t="n">
         <v>-2.0176</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G27" t="n">
         <v>-3.1631</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H27" t="n">
         <v>-5.8634</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I27" t="n">
         <v>2.7003</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J27" t="n">
         <v>12.3612</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K27" t="n">
         <v>8.307799999999999</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L27" t="n">
         <v>4.053399999999999</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M27" t="n">
         <v>-15.5242</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N27" t="n">
         <v>-14.1711</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O27" t="n">
         <v>-1.3532</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P27" t="n">
         <v>-6.837</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q27" t="n">
         <v>-17.5808</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R27" t="n">
         <v>10.7438</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S27" t="n">
         <v>0.9080999999999999</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T27" t="n">
         <v>-3.6856</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U27" t="n">
         <v>4.5932</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V27" t="n">
         <v>4.0977</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W27" t="n">
         <v>5.9285</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X27" t="n">
         <v>-1.8309</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
